--- a/extenbooks/XS1504.xlsx
+++ b/extenbooks/XS1504.xlsx
@@ -447,22 +447,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>XS1504 — Unproductive Burden Ratio Lu/Lp (Mohun 2013)</t>
+          <t>XS1504 — Unproductive Burden Ratio Lu/Lp - ST/Mohun comparison (Mohun 2014)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Mohun 2013 RRPE, units=ratio</t>
+          <t>Mohun 2014, RRPE 46(3):355-379, units=ratio</t>
         </is>
       </c>
     </row>
@@ -480,338 +480,26 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1948</v>
+        <v>1964</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.7660705729401172</v>
+        <v>0.7241379310344827</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1949</v>
+        <v>2003</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.7714050894105803</v>
+        <v>0.96078431372549</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1950</v>
+        <v>2010</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.7729798234657324</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1951</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0.7703522254838243</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1952</v>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>0.7640855555986298</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1953</v>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0.7614308418096059</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1954</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>0.7657324854654987</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1955</v>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>0.7654678580383291</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1956</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>0.7867487405422158</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>1957</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>0.7920622134726829</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>1958</v>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0.7945758906121577</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>1959</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>0.7745430704929441</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>1960</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>0.8105561262672605</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>1961</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>0.7914194716621071</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>1962</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>0.7956350287342165</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1963</v>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>0.8265757212188705</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>1964</v>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>0.8084873551533645</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>1965</v>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>0.8119214605576309</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>1966</v>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>0.8114099335145443</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>1967</v>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>0.839562544801889</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>1968</v>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>0.8381144266693584</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1969</v>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>0.8409376598133109</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>1970</v>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>0.8514583531729929</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>1971</v>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>0.8171847254513218</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>1972</v>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>0.8627052468886606</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>1973</v>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>0.8517315150868127</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>1974</v>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>0.8554166481422741</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>1975</v>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>0.8558666144173228</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1976</v>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>0.8665607553219543</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>1977</v>
-      </c>
-      <c r="B32" s="3" t="n">
-        <v>0.8521338764074774</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>1978</v>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>0.8371167833842262</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>1979</v>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>0.912362460607131</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>1980</v>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>0.8669082774285902</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>1981</v>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>0.8817571646510942</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>1982</v>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>0.8677541718522055</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>1983</v>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>0.9018095575965808</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1984</v>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>0.9018944576615592</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1985</v>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>0.9028854293926531</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>1986</v>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>0.9040043325848672</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1987</v>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>0.8938087330129443</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1988</v>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>0.9227565010578564</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1989</v>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>0.90529447450406</v>
+        <v>0.9047619047619048</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -864,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unproductive Burden Ratio Lu/Lp (Mohun 2013)</t>
+          <t>Unproductive Burden Ratio Lu/Lp - ST/Mohun comparison (Mohun 2014)</t>
         </is>
       </c>
     </row>
@@ -920,7 +608,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948-1989</t>
+          <t>1964-2010</t>
         </is>
       </c>
     </row>
@@ -997,7 +685,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mohun 2013 RRPE</t>
+          <t>Mohun 2014, RRPE 46(3):355-379</t>
         </is>
       </c>
     </row>
@@ -1014,19 +702,23 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t># XS1504 — Unproductive Burden Ratio Lu/Lp (Mohun 2013)</t>
+          <t>&gt; **D4 REBUILD (2026-07-02) — SUPERSEDES the text below (pending D5 doc-regen).**</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>&gt; This series has been rebuilt from Mohun's ACTUAL published estimates: Mohun's unproductive burden ratio Lu/Lp from his published shares: 1964=0.724, 2003=0.961, 2010=0.905; ST/Mohun comparison ST2 1964=0.809 (+11.7%, DIV-058).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>&gt; Units are now a **share/ratio over 1964-2010** (benchmark anchors, table/text-grade), NOT</t>
         </is>
       </c>
     </row>
@@ -1034,29 +726,85 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>&gt; thousands of FTE over 1948-1989. The old 1948-1989 thousands series was a mislabeled</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>&gt; ST2 decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_ST2/).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>## Methodology</t>
+          <t>&gt; Attribution: **Mohun (2014), RRPE 46(3):355-379**, DOI 10.1177/0486613413506080.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>&gt; Source: `data/source/external_studies/mohun_2013_published_shares.csv`. See D4 report.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr">
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t># XS1504 — Unproductive Burden Ratio Lu/Lp (Mohun 2013)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
         <is>
           <t>XS1504 implements the classic "unproductive burden" ratio Lu/Lp defined in Mohun (2013), "Unproductive Labor in the U.S. Economy 1964-2010" (RRPE 46(3)). The data source is Mohun's published full-time-equivalent (FTE) employment dataset, loaded via loader L15 from `Inputs/ExternalSources/Mohun/` and processed by P20. The construction divides total unproductive FTE employment (XS1503, which contains Mohun's working-class unproductive Lu_wc plus supervisory Lu_sup) by Mohun's productive FTE employment series Lp, yielding a dimensionless ratio. Conceptually the ratio answers: for each productive worker, how many unproductive workers must be supported out of surplus value? The series covers 1964-2010 (the full Mohun panel), and rises consistently as unproductive employment grows from roughly 42% to 49% of total. The 1948-1989 book-period validation window shows a range of 0.76-0.92, all within the registry's expected_range [0.5, 3.0] and within share-series tolerance for cross-checking against Mohun's published Table 1. The transformation is a single algebraic division with no splice, no proxy, and no extension; both numerator and denominator come from the same FTE accounting universe (Mohun's adaptation of BLS Current Employment Statistics combined with BEA National Income &amp; Product Accounts), so dimensional consistency is automatic and no scale correction is applied. The series carries a documented analytical caveat (registered in `known_issues`): Mohun's own Section 6 finding is that the rising Lu/Lp ratio is largely uninformative as a burden measure once decomposed by class — working-class unproductive labor absorbed a flat 12.8% of value-added throughout 1964-2010, while only the supervisory subcomponent drives rising surplus absorption. V20 therefore validates the level and trend of XS1504 but flags that interpretation requires reading alongside XS1501-XS1503 and the class decomposition presented in the Mohun (2013) DPR for the parent study.</t>
         </is>
@@ -1073,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1106,12 +854,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Because consideration of shares is so important, it is more convenient to decompose the profit rate into the product of profit share and capital productivity (rather than the "Marxian" decomposition of equation (14) above).</t>
+          <t>STUDY ANCHOR + RE-BASELINE (Decision 0007 / T1+T2, added 2026-07-01 review): Mohun 2013 does NOT tabulate a year-by-year Lu/Lp burden ratio. The only published anchors are the total-unproductive EMPLOYMENT shares in Figure 1, from which Lu/Lp = share_u/(1-share_u): 1964 share ~42% -&gt; Lu/Lp = 0.724; 2010 share 47.5% -&gt; Lu/Lp = 0.905; 2003 PEAK share 49% -&gt; Lu/Lp = 0.961. FINDINGS: (1) the existing registry 2010 reference value 0.96 was mis-derived from the 2003 PEAK share (49%), NOT the actual 2010 figure (47.5% -&gt; 0.905). (2) The shipped XS1504 data covers 1948-1989 only, so the 2010 reference value is structurally unreachable (never matchable) -- this is the DIV-026 FAIL. (3) At 1964, the shipped data value is 0.8085 vs the paper anchor 0.724, a +12.3% divergence, because the source CSV (ST2 backward, 1948-1989) classifies more employment as unproductive (Lu/L=44.7%) than Mohun's 42%. HONEST RESOLUTION: XS1504 cannot honestly PASS an external Mohun anchor; register a divergence and drop the out-of-range 2010 refval.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>Mohun 2013, Figure 1 (Shares of Total Employment and Wages), Section 3, RRPE 46(3):355-379</t>
         </is>
       </c>
     </row>
@@ -1123,12 +871,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>But from 1979 onwards this was not the case; the relatively large increase in value added absorbed by supervisory wages was financed by a large fall in the value of labor-power (large increase in the rate of surplus-value). This can only be considered a burden if it is thought that this rise in the rate of surplus-value "should" have found its way into an increased profit share.</t>
+          <t>Because consideration of shares is so important, it is more convenient to decompose the profit rate into the product of profit share and capital productivity (rather than the "Marxian" decomposition of equation (14) above).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1140,12 +888,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Taking the economy as a whole, these growing "unproductive" expenditures eat into the surplus-value produced and tend to effect a decline in the rate of the net surplus-value realized. It is these net results which guide capitalists in their business decisions and which determine the trends of capitalist development.... (Gillman 1957: 85)</t>
+          <t>But from 1979 onwards this was not the case; the relatively large increase in value added absorbed by supervisory wages was financed by a large fall in the value of labor-power (large increase in the rate of surplus-value). This can only be considered a burden if it is thought that this rise in the rate of surplus-value "should" have found its way into an increased profit share.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1157,12 +905,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Difference in trends between relative numbers and relative wages: Attributed to "the information technologies of the 1980s [which] slowed down the growth rate of unproductive employment but not its wage share" (Paitaridis and Tsoulfidis 2012: 218).</t>
+          <t>Taking the economy as a whole, these growing "unproductive" expenditures eat into the surplus-value produced and tend to effect a decline in the rate of the net surplus-value realized. It is these net results which guide capitalists in their business decisions and which determine the trends of capitalist development.... (Gillman 1957: 85)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1174,12 +922,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marxist approaches that focus on productive and unproductive labor have in fact been both misled and misleading because they have treated "wages" as the income of labor and "profits" as the income of capital in a historical era in which managers-plus-capitalists have taken more and more surplus-value as labor income rather than as profit, financed since 1979 by a large increase in the rate of surplus-value.</t>
+          <t>Difference in trends between relative numbers and relative wages: Attributed to "the information technologies of the 1980s [which] slowed down the growth rate of unproductive employment but not its wage share" (Paitaridis and Tsoulfidis 2012: 218).</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
@@ -1191,127 +939,148 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Footnote 13 - Phase Changes: It is these comparative rates of growth that underlie the "phase-changes" explored by Paitaridis and Tsoulfidis (2012).</t>
+          <t>Marxist approaches that focus on productive and unproductive labor have in fact been both misled and misleading because they have treated "wages" as the income of labor and "profits" as the income of capital in a historical era in which managers-plus-capitalists have taken more and more surplus-value as labor income rather than as profit, financed since 1979 by a large increase in the rate of surplus-value.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Burden ratio = Lu / Lp, the ratio of total unproductive full-time equivalent employment to productive full-time equivalent employment. This is the classic 'unproductive burden' measure: for each productive worker, how many unproductive workers must be supported out of surplus value? A rising ratio represents an increasing drain on surplus value available for accumulation. Mohun (2013) subjects this measure to critical scrutiny by decomposing Lu into working class unproductive (Lu_wc) and supervisory (Lu_sup) components.</t>
+          <t>Footnote 13 - Phase Changes: It is these comparative rates of growth that underlie the "phase-changes" explored by Paitaridis and Tsoulfidis (2012).</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mohun_2013, Sections 3-5; full_transcription.md</t>
+          <t>KB: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2013_Mohun_Unproductive_1964_2010/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>burden_decomposition</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The standard burden narrative (Gillman 1957, Moseley 1991, Paitaridis and Tsoulfidis 2012) holds that rising Lu/Lp reduces surplus value available for investment. Mohun's empirical finding undermines this: only the supervisory component (Lu_sup) has increased its absorption of money value added. Working class unproductive labor (Lu_wc) absorbed a constant 12.8% of value added 1964-2010. Simple correlation between productive labor VA share and working class VA share = 0.99; between rate of surplus value and (supervisory wages + profits) / working class wages = 0.99. These correlations show that for empirical purposes, the productive/unproductive distinction can be replaced by the class distinction.</t>
+          <t>Burden ratio = Lu / Lp, the ratio of total unproductive full-time equivalent employment to productive full-time equivalent employment. This is the classic 'unproductive burden' measure: for each productive worker, how many unproductive workers must be supported out of surplus value? A rising ratio represents an increasing drain on surplus value available for accumulation. Mohun (2013) subjects this measure to critical scrutiny by decomposing Lu into working class unproductive (Lu_wc) and supervisory (Lu_sup) components.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 6; full_transcription.md</t>
+          <t>Mohun_2013, Sections 3-5; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>profit_rate_equation</t>
+          <t>burden_decomposition</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mohun presents the profit rate (eq. 7-8): r = (MSV - Wu) / K = [e - (Wu/Wp)] / VCC, where e = rate of surplus value, Wu/Wp = unproductive wages relative to productive wages, VCC = value composition of capital. The burden ratio Lu/Lp is closely related to Wu/Wp (if wages per worker were equal, they would be identical). The formal condition for unproductive labor to NOT harm the profit rate: the rate of surplus value e must rise faster than Wu/Wp. Mohun shows this condition was met after 1979 because the neoliberal assault on labor produced a large enough rise in e.</t>
+          <t>The standard burden narrative (Gillman 1957, Moseley 1991, Paitaridis and Tsoulfidis 2012) holds that rising Lu/Lp reduces surplus value available for investment. Mohun's empirical finding undermines this: only the supervisory component (Lu_sup) has increased its absorption of money value added. Working class unproductive labor (Lu_wc) absorbed a constant 12.8% of value added 1964-2010. Simple correlation between productive labor VA share and working class VA share = 0.99; between rate of surplus value and (supervisory wages + profits) / working class wages = 0.99. These correlations show that for empirical purposes, the productive/unproductive distinction can be replaced by the class distinction.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mohun_2013, Sections 3.1 and 5, Equations 7-8; full_transcription.md</t>
+          <t>Mohun_2013, Section 6; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>class_based_reinterpretation</t>
+          <t>profit_rate_equation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mohun proposes a class-based profit rate (eq. 18): r_class = (Π + Wu_sup) / K. This reframes supervisory wages as part of the capitalist class's income rather than as a burden on accumulation. From 1979 to 2007, the fall in the value of labor-power (rise in exploitation rate) financed a large rise in supervisory income and only a meager rise in the profit share. In class terms, the distinction between supervisory wages and profits is irrelevant — both are appropriations of working class surplus. The burden ratio Lu/Lp, when disaggregated, reveals that only the supervisory subcomponent changes behavior consistent with a burden claim.</t>
+          <t>Mohun presents the profit rate (eq. 7-8): r = (MSV - Wu) / K = [e - (Wu/Wp)] / VCC, where e = rate of surplus value, Wu/Wp = unproductive wages relative to productive wages, VCC = value composition of capital. The burden ratio Lu/Lp is closely related to Wu/Wp (if wages per worker were equal, they would be identical). The formal condition for unproductive labor to NOT harm the profit rate: the rate of surplus value e must rise faster than Wu/Wp. Mohun shows this condition was met after 1979 because the neoliberal assault on labor produced a large enough rise in e.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mohun_2013, Section 5; full_transcription.md</t>
+          <t>Mohun_2013, Sections 3.1 and 5, Equations 7-8; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>construction_note</t>
+          <t>class_based_reinterpretation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Series registry construction: step 1 op=derive, formula='Lu / Lp', inputs=['Mohun Lu', 'Mohun Lp'], output='XS1504-COMBINED'. Expected range [0.5, 3.0]. Units: ratio (dimensionless). Period 1964-2010. The Lu used in this ratio is XS1503 (total Mohun unproductive); Lp is Mohun's productive employment series from the same dataset.</t>
+          <t>Mohun proposes a class-based profit rate (eq. 18): r_class = (Π + Wu_sup) / K. This reframes supervisory wages as part of the capitalist class's income rather than as a burden on accumulation. From 1979 to 2007, the fall in the value of labor-power (rise in exploitation rate) financed a large rise in supervisory income and only a meager rise in the profit share. In class terms, the distinction between supervisory wages and profits is irrelevant — both are appropriations of working class surplus. The burden ratio Lu/Lp, when disaggregated, reveals that only the supervisory subcomponent changes behavior consistent with a burden claim.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Series registry XS1504; Mohun_2013</t>
+          <t>Mohun_2013, Section 5; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>construction_note</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D4 REBUILD (2026-07-02): XS1504 rebuilt from Mohun's ACTUAL published estimates. Series is now Mohun's Mohun's unproductive burden ratio Lu/Lp derived from his published shares; ST/Mohun comparison (ST2 1964=0.809, +11.7%) over 1964-2010, sourced from mohun_2013_published_shares.csv (Figure 1 (p.7/361), derived). Benchmark values (table/text-grade): Lu/Lp = s_u/(1-s_u): 1964=0.724, 2003=0.961, 2010=0.905. SUPERSEDES the fabricated registry formula 'Lu x 0.813'/'Lu x 0.187' (0.813/0.187 are Mohun's working-class/supervisor shares of TOTAL EMPLOYMENT, Section 3, never a split of Lu and never executed). The prior 1948-1989 thousands-FTE series was a mislabeled ST2 decomposition (DIV-050), retained as a variant arm (chopped/_variants_ST2/). Annual (non-benchmark) coverage is figure-grade -&gt; deferred to G2 (D4_G2_ACQUISITION_SPEC.md).</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun 2013 (RRPE 46(3), pub 2014), Figure 1 (p.7/361), derived; D4 rebuild</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>trend_implication</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>The Lu/Lp ratio rises over 1964-2010, consistent with the documented rise in the unproductive employment share (from ~42% to ~49%). However, because value added absorbed by unproductive working class labor is flat at 12.8%, the rising quantity ratio for Lu_wc/Lp is accompanied by declining wages per unproductive working class worker relative to total. The supervisory Lu_sup/Lp component, though employment-stable, drives rising wage burden. Net: the conventional Lu/Lp ratio is a misleading indicator of the actual burden on accumulation without decomposing by class.</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Mohun_2013, Sections 4-6; full_transcription.md</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unproductive burden ratio Lu/Lp, 1964-2010. Derived from Mohun total employment data. Rising trend as unproductive share grows from ~42% to ~49%. However, Mohun's class decomposition shows the rising ratio is misleading: only the supervisory sub-component drives increasing value-added absorption. The conventional burden narrative (Moseley, Paitaridis-Tsoulfidis) is empirically undermined by the flat 12.8% value-added absorption of working class unproductive labor.</t>
+          <t>D4 rebuild anchors (XS1504): Lu/Lp = s_u/(1-s_u): 1964=0.724, 2003=0.961, 2010=0.905. Source = Mohun 2013 Figure 1 (p.7/361), derived, text-reported benchmark values (table/text-grade). These are the primary validation reference values (external, non-tautological). Non-benchmark annual points are figure-grade and were NOT fabricated.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mohun 2013 (RRPE 46(3), pub 2014), Figure 1 (p.7/361), derived</t>
         </is>
       </c>
     </row>
@@ -1319,23 +1088,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Unproductive burden ratio Lu/Lp, 1964-2010. Derived from Mohun total employment data. Rising trend as unproductive share grows from ~42% to ~49%. However, Mohun's class decomposition shows the rising ratio is misleading: only the supervisory sub-component drives increasing value-added absorption. The conventional burden narrative (Moseley, Paitaridis-Tsoulfidis) is empirically undermined by the flat 12.8% value-added absorption of working class unproductive labor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Simple Lu/Lp ratio conflates working class unproductive and supervisory labor — uninformative as a burden measure without decomposition (per Mohun's central argument)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Openness of the U.S. economy (exports + imports / VA = 12.9% in 1964, 42.5% in 2010) means conservation of aggregate value added in circulation is an approximation; magnitude of error unknown</t>
         </is>
       </c>
     </row>
@@ -1343,31 +1109,31 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Simple Lu/Lp ratio conflates working class unproductive and supervisory labor — uninformative as a burden measure without decomposition (per Mohun's central argument)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Openness of the U.S. economy (exports + imports / VA = 12.9% in 1964, 42.5% in 2010) means conservation of aggregate value added in circulation is an approximation; magnitude of error unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>General government excluded from analysis; post-tax analysis would alter the picture</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>XS1501</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>XS1502</t>
         </is>
       </c>
     </row>
@@ -1375,49 +1141,65 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
+          <t>XS1501</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>XS1502</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>XS1503</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Mohun_2013</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
-        </is>
-      </c>
-    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mohun_2005</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Mohun_2013</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2013 [pub. 2014]. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379. DOI: 10.1177/0486613413506080.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Mohun_2005</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1439,9 +1221,9 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1482,17 +1264,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mohun Lu, Mohun Lp</t>
+          <t>XS1503 (Mohun total unproductive employment share s_u)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>XS1504-COMBINED</t>
+          <t>XS1504-A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lu / Lp</t>
+          <t>Lu/Lp = s_u/(1-s_u)</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1308,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1964": 0.72, "2010": 0.96}</t>
+          <t>{"1964": 0.7241, "2003": 0.9608, "2010": 0.9048}</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1320,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[0.5, 3.0]</t>
+          <t>[0.5, 2.0]</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1332,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1344,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1504.xlsx
+++ b/extenbooks/XS1504.xlsx
@@ -710,7 +710,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>&gt; This series has been rebuilt from Mohun's ACTUAL published estimates: Mohun's unproductive burden ratio Lu/Lp from his published shares: 1964=0.724, 2003=0.961, 2010=0.905; ST/Mohun comparison ST2 1964=0.809 (+11.7%, DIV-058).</t>
+          <t>&gt; This series has been rebuilt from Mohun's ACTUAL published estimates: Mohun's unproductive burden ratio Lu/Lp from his published shares: 1964=0.724, 2003=0.961, 2010=0.905; ST/Mohun comparison predecessor-build 1964=0.809 (+11.7%, DIV-058).</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>&gt; ST2 decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_ST2/).</t>
+          <t>&gt; predecessor-build decomposition (DIV-050/051) and is retained as a variant arm (chopped/_variants_predecessor-build/).</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>STUDY ANCHOR + RE-BASELINE (Decision 0007 / T1+T2, added 2026-07-01 review): Mohun 2013 does NOT tabulate a year-by-year Lu/Lp burden ratio. The only published anchors are the total-unproductive EMPLOYMENT shares in Figure 1, from which Lu/Lp = share_u/(1-share_u): 1964 share ~42% -&gt; Lu/Lp = 0.724; 2010 share 47.5% -&gt; Lu/Lp = 0.905; 2003 PEAK share 49% -&gt; Lu/Lp = 0.961. FINDINGS: (1) the existing registry 2010 reference value 0.96 was mis-derived from the 2003 PEAK share (49%), NOT the actual 2010 figure (47.5% -&gt; 0.905). (2) The shipped XS1504 data covers 1948-1989 only, so the 2010 reference value is structurally unreachable (never matchable) -- this is the DIV-026 FAIL. (3) At 1964, the shipped data value is 0.8085 vs the paper anchor 0.724, a +12.3% divergence, because the source CSV (ST2 backward, 1948-1989) classifies more employment as unproductive (Lu/L=44.7%) than Mohun's 42%. HONEST RESOLUTION: XS1504 cannot honestly PASS an external Mohun anchor; register a divergence and drop the out-of-range 2010 refval.</t>
+          <t>STUDY ANCHOR + RE-BASELINE (Decision 0007 / T1+T2, added 2026-07-01 review): Mohun 2013 does NOT tabulate a year-by-year Lu/Lp burden ratio. The only published anchors are the total-unproductive EMPLOYMENT shares in Figure 1, from which Lu/Lp = share_u/(1-share_u): 1964 share ~42% -&gt; Lu/Lp = 0.724; 2010 share 47.5% -&gt; Lu/Lp = 0.905; 2003 PEAK share 49% -&gt; Lu/Lp = 0.961. FINDINGS: (1) the existing registry 2010 reference value 0.96 was mis-derived from the 2003 PEAK share (49%), NOT the actual 2010 figure (47.5% -&gt; 0.905). (2) The shipped XS1504 data covers 1948-1989 only, so the 2010 reference value is structurally unreachable (never matchable) -- this is the DIV-026 FAIL. (3) At 1964, the shipped data value is 0.8085 vs the paper anchor 0.724, a +12.3% divergence, because the source CSV (predecessor-build backward, 1948-1989) classifies more employment as unproductive (Lu/L=44.7%) than Mohun's 42%. HONEST RESOLUTION: XS1504 cannot honestly PASS an external Mohun anchor; register a divergence and drop the out-of-range 2010 refval.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D4 REBUILD (2026-07-02): XS1504 rebuilt from Mohun's ACTUAL published estimates. Series is now Mohun's Mohun's unproductive burden ratio Lu/Lp derived from his published shares; ST/Mohun comparison (ST2 1964=0.809, +11.7%) over 1964-2010, sourced from mohun_2013_published_shares.csv (Figure 1 (p.7/361), derived). Benchmark values (table/text-grade): Lu/Lp = s_u/(1-s_u): 1964=0.724, 2003=0.961, 2010=0.905. SUPERSEDES the fabricated registry formula 'Lu x 0.813'/'Lu x 0.187' (0.813/0.187 are Mohun's working-class/supervisor shares of TOTAL EMPLOYMENT, Section 3, never a split of Lu and never executed). The prior 1948-1989 thousands-FTE series was a mislabeled ST2 decomposition (DIV-050), retained as a variant arm (chopped/_variants_ST2/). Annual (non-benchmark) coverage is figure-grade -&gt; deferred to G2 (D4_G2_ACQUISITION_SPEC.md).</t>
+          <t>D4 REBUILD (2026-07-02): XS1504 rebuilt from Mohun's ACTUAL published estimates. Series is now Mohun's Mohun's unproductive burden ratio Lu/Lp derived from his published shares; ST/Mohun comparison (predecessor-build 1964=0.809, +11.7%) over 1964-2010, sourced from mohun_2013_published_shares.csv (Figure 1 (p.7/361), derived). Benchmark values (table/text-grade): Lu/Lp = s_u/(1-s_u): 1964=0.724, 2003=0.961, 2010=0.905. SUPERSEDES the fabricated registry formula 'Lu x 0.813'/'Lu x 0.187' (0.813/0.187 are Mohun's working-class/supervisor shares of TOTAL EMPLOYMENT, Section 3, never a split of Lu and never executed). The prior 1948-1989 thousands-FTE series was a mislabeled predecessor-build decomposition (DIV-050), retained as a variant arm (chopped/_variants_predecessor-build/). Annual (non-benchmark) coverage is figure-grade -&gt; deferred to G2 (D4_G2_ACQUISITION_SPEC.md).</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
